--- a/web/public/forms/jikjeop-sigong-gyehoek.xlsx
+++ b/web/public/forms/jikjeop-sigong-gyehoek.xlsx
@@ -655,7 +655,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="32" t="inlineStr">

--- a/web/public/forms/jikjeop-sigong-gyehoek.xlsx
+++ b/web/public/forms/jikjeop-sigong-gyehoek.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접시공계획서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'직접시공계획서'!$A$1:$H$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$H$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -268,9 +266,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -883,19 +878,13 @@
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="7" t="n"/>
-      <c r="E16" s="11">
-        <f>IF(N(B16)=0,"",B16)</f>
-        <v/>
-      </c>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="12">
-        <f>IF(AND(N(B15)&gt;0,N(E15)&gt;0,E15&lt;B15),"⚠ 착공일이 계약일보다 앞섭니다.",IF(AND(N(E15)&gt;0,N(G15)&gt;0,G15&lt;E15),"⚠ 준공예정일이 착공일보다 앞섭니다.",""))</f>
-        <v/>
-      </c>
+      <c r="A17" s="12" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -1005,10 +994,7 @@
           <t>의무 비율(시행령 제30조의2)</t>
         </is>
       </c>
-      <c r="J23" s="18">
-        <f>IF(N(J22)=0,"",IF(J22&lt;300000000,0.5,IF(J22&lt;1000000000,0.3,IF(J22&lt;3000000000,0.2,IF(J22&lt;7000000000,0.1,"대상 아님")))))</f>
-        <v/>
-      </c>
+      <c r="J23" s="18" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="6" t="n"/>
@@ -1024,10 +1010,7 @@
           <t>직접시공 비율(⑦÷⑤)</t>
         </is>
       </c>
-      <c r="J24" s="19">
-        <f>IF(OR(N(B16)=0,N(C35)=0),"",C35/B16)</f>
-        <v/>
-      </c>
+      <c r="J24" s="19" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="6" t="n"/>
@@ -1043,10 +1026,7 @@
           <t>판    정</t>
         </is>
       </c>
-      <c r="J25" s="20">
-        <f>IF(OR(N(J22)=0,J24=""),"",IF(J23="대상 아님","대상 아님",IF(J24&gt;=J23,"충족","부족")))</f>
-        <v/>
-      </c>
+      <c r="J25" s="20" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="6" t="n"/>
@@ -1151,10 +1131,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n"/>
-      <c r="C35" s="23">
-        <f>SUM(C21:C34)</f>
-        <v/>
-      </c>
+      <c r="C35" s="23" t="n"/>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="22" t="inlineStr">
         <is>
@@ -1163,17 +1140,11 @@
         </is>
       </c>
       <c r="F35" s="7" t="n"/>
-      <c r="G35" s="23">
-        <f>SUM(G21:G34)</f>
-        <v/>
-      </c>
+      <c r="G35" s="23" t="n"/>
       <c r="H35" s="7" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="12">
-        <f>IF(AND(N(B16)&gt;0,C35+G35&gt;0,ABS(C35+G35-B16)&gt;=1),"⚠ ⑦+⑧ = "&amp;TEXT(C35+G35,"#,##0")&amp;"원 — ⑤총 노무비("&amp;TEXT(B16,"#,##0")&amp;"원)와 다릅니다.","")&amp;IF(J25="부족","  ⚠ 직접시공 비율이 의무 비율보다 낮습니다(오른쪽 도움 칸).","")</f>
-        <v/>
-      </c>
+      <c r="A36" s="12" t="n"/>
     </row>
     <row r="37" ht="6" customHeight="1"/>
     <row r="38" ht="24" customHeight="1">
@@ -1198,10 +1169,7 @@
           <t>통보인(수급인)</t>
         </is>
       </c>
-      <c r="F41" s="28">
-        <f>TRIM(C10&amp;" "&amp;F10)</f>
-        <v/>
-      </c>
+      <c r="F41" s="28" t="n"/>
       <c r="H41" s="29" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
@@ -1210,10 +1178,7 @@
     </row>
     <row r="42" ht="6" customHeight="1"/>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="30">
-        <f>IF(F7="","                              귀하",F7&amp;" 귀하")</f>
-        <v/>
-      </c>
+      <c r="A43" s="30" t="n"/>
     </row>
     <row r="44" ht="8" customHeight="1"/>
     <row r="45" ht="26" customHeight="1">
@@ -1234,6 +1199,7 @@
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="7" t="n"/>
     </row>
+    <row r="46"/>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
@@ -1381,819 +1347,4 @@
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="F1" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>■ 건설산업기본법 시행규칙 [별지 제22호의6서식]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>건설공사의 직접시공계획서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="4" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>①공  종</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>토목</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>현장소재지</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 다라동 123-4 일원</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>발 주 자</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>상호(기관명)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>가나시</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>대 표 자</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>가나시장</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>구    분</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>[ ∨ ] 공공기관          [    ] 민간</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>가나시 가나로 1</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>수 급 인</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>상    호</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>대 표 자</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>영업소 소재지</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>도급방법</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>[ ∨ ] 단독도급</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>[    ] 공동도급</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>계약성질</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>[    ] 장기계속공사          [ ∨ ] 기타공사</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>②계 약 일</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>46083</v>
-      </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>③착 공 일</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>46090</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>④준공
-예정일</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="H15" s="7" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>⑤총 노무비</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>287500000</v>
-      </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="11">
-        <f>IF(N(B16)=0,"",B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-    </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="12">
-        <f>IF(AND(N(B15)&gt;0,N(E15)&gt;0,E15&lt;B15),"⚠ 착공일이 계약일보다 앞섭니다.",IF(AND(N(E15)&gt;0,N(G15)&gt;0,G15&lt;E15),"⚠ 준공예정일이 착공일보다 앞섭니다.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>직 접 시 공 계 획</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>직접시공 공종 (기능인력 투입예정 인원 :</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>하도급(예정) 공종</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>⑥세부공종</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>금    액</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>⑥세부공종</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>금    액</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>토공(터파기·되메우기)</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="16" t="n">
-        <v>42300000</v>
-      </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>구조물공(암거)</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="16" t="n">
-        <v>85500000</v>
-      </c>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>직접시공 비율 확인 (인쇄 안 됨)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>배수공(관 부설)</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="16" t="n">
-        <v>38700000</v>
-      </c>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>포장공</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="16" t="n">
-        <v>94000000</v>
-      </c>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>도급금액</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>963241000</v>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>부대공</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="16" t="n">
-        <v>12400000</v>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>의무 비율(시행령 제30조의2)</t>
-        </is>
-      </c>
-      <c r="J23" s="18">
-        <f>IF(N(J22)=0,"",IF(J22&lt;300000000,0.5,IF(J22&lt;1000000000,0.3,IF(J22&lt;3000000000,0.2,IF(J22&lt;7000000000,0.1,"대상 아님")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>간접노무비</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="16" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>직접시공 비율(⑦÷⑤)</t>
-        </is>
-      </c>
-      <c r="J24" s="19">
-        <f>IF(OR(N(B16)=0,N(C35)=0),"",C35/B16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>판    정</t>
-        </is>
-      </c>
-      <c r="J25" s="20">
-        <f>IF(OR(N(J22)=0,J24=""),"",IF(J23="대상 아님","대상 아님",IF(J24&gt;=J23,"충족","부족")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>3억 미만 50% · 3억~10억 30% · 10억~30억 20% · 30억~70억 10% (노무비 기준) · 70억 이상은 직접시공 의무 대상 아님</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="7" t="n"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="7" t="n"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="7" t="n"/>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="7" t="n"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="7" t="n"/>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="7" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="22" t="inlineStr">
-        <is>
-          <t>⑦직접시공 금액 합계
-(직접시공 노무비)</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="23">
-        <f>SUM(C21:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>⑧하도급(예정)
-금액 합계</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="23">
-        <f>SUM(G21:G34)</f>
-        <v/>
-      </c>
-      <c r="H35" s="7" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="12">
-        <f>IF(AND(N(B16)&gt;0,C35+G35&gt;0,ABS(C35+G35-B16)&gt;=1),"⚠ ⑦+⑧ = "&amp;TEXT(C35+G35,"#,##0")&amp;"원 — ⑤총 노무비("&amp;TEXT(B16,"#,##0")&amp;"원)와 다릅니다.","")&amp;IF(J25="부족","  ⚠ 직접시공 비율이 의무 비율보다 낮습니다(오른쪽 도움 칸).","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>「건설산업기본법」 제28조의2에 따라 건설공사의 직접시공계획을 통보합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="4" customHeight="1"/>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="25" t="n">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="26" t="inlineStr"/>
-      <c r="D41" s="27" t="inlineStr">
-        <is>
-          <t>통보인(수급인)</t>
-        </is>
-      </c>
-      <c r="F41" s="28">
-        <f>TRIM(C10&amp;" "&amp;F10)</f>
-        <v/>
-      </c>
-      <c r="H41" s="29" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="30">
-        <f>IF(F7="","                              귀하",F7&amp;" 귀하")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>구비서류</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>직접 시공 및 하도급 할 공사량ㆍ공사단가 및 공사금액(노무비)이 명시된 공사내역서</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-    </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="103">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="I26:J28"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="E21:F21"/>
-  </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"[ ∨ ] 공공기관          [    ] 민간,[    ] 공공기관          [ ∨ ] 민간"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"[ ∨ ] 단독도급,[    ] 단독도급"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"[    ] 공동도급,[ ∨ ] 공동도급 ( 공동이행방식 ),[ ∨ ] 공동도급 ( 분담이행방식 ),[ ∨ ] 공동도급 ( 주계약자관리방식 )"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"[ ∨ ] 장기계속공사          [    ] 기타공사,[    ] 장기계속공사          [ ∨ ] 기타공사"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/jikjeop-sigong-gyehoek.xlsx
+++ b/web/public/forms/jikjeop-sigong-gyehoek.xlsx
@@ -650,7 +650,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
